--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0065.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0065.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Energy Regen+</t>
+          <t>Hồi Năng Lượng+</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Healing+</t>
+          <t>Tăng Hiệu Quả Hồi Phục +10%.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Energy Regen+</t>
+          <t>Hồi Năng Lượng+</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Max HP+</t>
+          <t>HP tối đa+</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cơn Thịnh Nộ Của Vực Sâu</t>
+          <t>Wrath of the Deep</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Energy Regen+</t>
+          <t>Hồi Năng Lượng+</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aero DMG+</t>
+          <t>Sát Thương Aero+</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Cơn Gió Trên Thiên Không</t>
+          <t>Gusts of Welkin</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Aero DMG+</t>
+          <t>Sát Thương Aero+</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Fusion DMG+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Giấc Mơ Của Kẻ Lạc Lối</t>
+          <t>Dream of the Lost</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Glacio DMG+</t>
+          <t>Tấn Công Băng giá tăng thêm 10%.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Vương Miện Dũng Khí</t>
+          <t>Crown of Valor</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Quy Luật Hòa Âm</t>
+          <t>Law of Harmony</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Sợi Chỉ Định Mệnh Đứt Đoạn</t>
+          <t>Thread of Severed Fate</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG</t>
+          <t>Sát Thương Spectro+</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Giao Ước Nhảy Ánh Neon</t>
+          <t>Pact of Neonlight Leap</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Healing+</t>
+          <t>Hồi phục+</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Vầng Hào Quang Sao Sáng</t>
+          <t>Halo of Starry Radiance</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG</t>
+          <t>Sát Thương Spectro+</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Nghi Lễ Khải Huyền Hoàng Kim</t>
+          <t>Rite of Gilded Revelation</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Fusion DMG+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Fusion DMG+</t>
+          <t>Tăng Sát Thương Fusion+</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Aero DMG+</t>
+          <t>Sát Thương Aero+</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Âm Thanh Của Danh Chân Thật</t>
+          <t>Sound of True Name</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Fusion DMG+</t>
+          <t>Sát Thương Hợp Thể +10%.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Electro DMG+</t>
+          <t>Sát Thương Electro +10%.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Aero DMG+</t>
+          <t>DMG Aero +10%.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Ước Nguyện Tuyết Lặng Im</t>
+          <t>Wishes of Quiet Snowfall</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Cuộn Ký Ức Đan Xen</t>
+          <t>Reel of Spliced Memories</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Glacio DMG+</t>
+          <t>Tăng Sát Thương Glacio</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG</t>
+          <t>Sát Thương Spectro +10%.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Mở Khóa Echo</t>
+          <t>Mở Khóa Tiếng Vọng</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Mở Khóa Ngoại Hình Ảo Ảnh</t>
+          <t>Mở khóa Ngoại Hình Ảo Ảnh.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Phantom Appearance</t>
+          <t>Hiện Hình Ảo Ảnh</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tune Break: Broadblade</t>
+          <t>Tune Break: Đại kiếm</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Tune Break: Pistols</t>
+          <t>Tune Break: Súng</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Tune Break: Gauntlets</t>
+          <t>Tune Break: Găng tay</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Tune Break: Rectifier</t>
+          <t>Tune Break: Pháp khí</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Starfield Calibrator</t>
+          <t>Điều Tần Sao Trời</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Moongazer's Sigil</t>
+          <t>Ấn Nguyệt Khán</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Thunderblaze Eminence</t>
+          <t>Thiên Sấm Chói Lọi</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Sợi Chỉ Số Mệnh</t>
+          <t>Sợi Dây Định Mệnh</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Definite Solution</t>
+          <t>Giải Pháp Dứt Khoát</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Lời Thề Của Thợ Săn Thủy Triều</t>
+          <t>Lời Thề Thợ Săn Thủy Triều</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Signal Catcher</t>
+          <t>Bộ bắt tín hiệu</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>When A Heart Settles</t>
+          <t>Khi Trái Tim An Yên</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Lời Thề Của Thợ Săn Thủy Triều</t>
+          <t>Lời Thề Thợ Săn Thủy Triều</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>To Fire Cô ấy Returns</t>
+          <t>Lửa Trở Về</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Insight Bearer</t>
+          <t>Người Mang Ánh Sáng Tri Thức</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Attendance Exemption Protocol</t>
+          <t>Giao Thức Miễn Trắc Nghiệm</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>When A Heart Settles</t>
+          <t>Khi Trái Tim An Yên</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Lời Thề Của Thợ Săn Thủy Triều</t>
+          <t>Lời Thề Thợ Săn Thủy Triều</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Cấp Độ</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Cooldown Reduction</t>
+          <t>Giảm thời gian hồi</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Tăng DMG Chung</t>
+          <t>General DMG Bonus</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Giảm DMG Chung</t>
+          <t>General DMG Reduction</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Kháng Glacio</t>
+          <t>Glacio RES</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Kháng Aero</t>
+          <t>Aero RES</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Mức tiêu hao STA khi Leo Nhanh x/Khung hình</t>
+          <t>Quick Climb Stamina Consumption x/Frame</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Loại Thuộc tính Nguyên tố</t>
+          <t>Elemental Attribute Type</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Climbing Nhảy Stamina Consumption (Once)</t>
+          <t>Climbing Jump Stamina Consumption (Once)</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Tốc độ tiêu hao STA khi Bay lượn x/Giây</t>
+          <t>Gliding Stamina Consumption Speed x/Second</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tốc độ di chuyển</t>
+          <t>Movement Speed</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>STA tiêu hao khi Nhảy Leo (mỗi lần)</t>
+          <t>Stamina Consumed by Climbing Jump (Once)</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Tốc độ tiêu hao STA khi Bay lượn x/giây</t>
+          <t>Gliding Stamina Consumption Speed x/second</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hệ số Ma sát</t>
+          <t>Coefficient of Friction</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Tốc độ di chuyển</t>
+          <t>Movement Speed</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Cooldown Reduction</t>
+          <t>Giảm thời gian hồi</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Tăng DMG Chung</t>
+          <t>General DMG Bonus</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Giảm DMG Chung</t>
+          <t>General DMG Reduction</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Đây là Cấp độ của bạn</t>
+          <t>This is your Level</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Cấp độ</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Kháng Glacio</t>
+          <t>Glacio RES</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Kháng Aero</t>
+          <t>Aero RES</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Barrier Breacher</t>
+          <t>Kẻ Phá Rào</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Plenilune Radiance</t>
+          <t>Ánh Trăng Tròn Rạng Rỡ</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Oath of Tide Hunters</t>
+          <t>Lời Thề Thợ Săn Thủy Triều</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Feather Edge</t>
+          <t>Lưỡi Kiếm Sắc Bén</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Path Observer</t>
+          <t>Người Quan Sát Con Đường</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Oath of Tide Hunters</t>
+          <t>Lời Thề Thợ Săn Thủy Triều</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Solar Flame</t>
+          <t>Lửa Mặt Trời</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Aether Strike</t>
+          <t>Đòn Đánh Aether</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Mức tiêu hao STA khi Leo Nhanh x/Khung hình</t>
+          <t>Quick Climb Stamina Consumption x/Frame</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Loại Thuộc tính Nguyên tố</t>
+          <t>Elemental Attribute Type</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
